--- a/artfynd/A 36109-2025 artfynd.xlsx
+++ b/artfynd/A 36109-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>127093757</v>
       </c>
       <c r="B2" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127093589</v>
       </c>
       <c r="B3" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>127093718</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>127093875</v>
       </c>
       <c r="B5" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,6 +1112,333 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127300607</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96039</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 36109, Sandvik, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>590863</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6418766</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127300654</v>
+      </c>
+      <c r="B7" t="n">
+        <v>105471</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 36109, Sandvik, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>590948</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6418715</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127300753</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98436</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A 36109, Sandvik, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>590923</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6418737</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2 blommor</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36109-2025 artfynd.xlsx
+++ b/artfynd/A 36109-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127093757</v>
       </c>
       <c r="B2" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127093589</v>
       </c>
       <c r="B3" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>127093718</v>
       </c>
       <c r="B4" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>127093875</v>
       </c>
       <c r="B5" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>127300607</v>
       </c>
       <c r="B6" t="n">
-        <v>96039</v>
+        <v>96045</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>127300654</v>
       </c>
       <c r="B7" t="n">
-        <v>105471</v>
+        <v>105477</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>127300753</v>
       </c>
       <c r="B8" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36109-2025 artfynd.xlsx
+++ b/artfynd/A 36109-2025 artfynd.xlsx
@@ -1217,41 +1217,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127300654</v>
+        <v>127300753</v>
       </c>
       <c r="B7" t="n">
-        <v>105477</v>
+        <v>98442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1260,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590948</v>
+        <v>590923</v>
       </c>
       <c r="R7" t="n">
-        <v>6418715</v>
+        <v>6418737</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,6 +1304,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2 blommor</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1323,49 +1336,41 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127300753</v>
+        <v>127300654</v>
       </c>
       <c r="B8" t="n">
-        <v>98442</v>
+        <v>105477</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1374,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590923</v>
+        <v>590948</v>
       </c>
       <c r="R8" t="n">
-        <v>6418737</v>
+        <v>6418715</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,11 +1415,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2 blommor</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 36109-2025 artfynd.xlsx
+++ b/artfynd/A 36109-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127093757</v>
       </c>
       <c r="B2" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127093589</v>
       </c>
       <c r="B3" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>127093718</v>
       </c>
       <c r="B4" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>127093875</v>
       </c>
       <c r="B5" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>127300607</v>
       </c>
       <c r="B6" t="n">
-        <v>96045</v>
+        <v>96046</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>127300753</v>
       </c>
       <c r="B7" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>127300654</v>
       </c>
       <c r="B8" t="n">
-        <v>105477</v>
+        <v>105478</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36109-2025 artfynd.xlsx
+++ b/artfynd/A 36109-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127093757</v>
       </c>
       <c r="B2" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127093589</v>
       </c>
       <c r="B3" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>127093718</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>127093875</v>
       </c>
       <c r="B5" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>127300607</v>
       </c>
       <c r="B6" t="n">
-        <v>96046</v>
+        <v>96050</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,49 +1217,41 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127300753</v>
+        <v>127300654</v>
       </c>
       <c r="B7" t="n">
-        <v>98443</v>
+        <v>105484</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1268,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590923</v>
+        <v>590948</v>
       </c>
       <c r="R7" t="n">
-        <v>6418737</v>
+        <v>6418715</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,11 +1296,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2 blommor</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,41 +1323,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127300654</v>
+        <v>127300753</v>
       </c>
       <c r="B8" t="n">
-        <v>105478</v>
+        <v>98447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1379,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590948</v>
+        <v>590923</v>
       </c>
       <c r="R8" t="n">
-        <v>6418715</v>
+        <v>6418737</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,6 +1410,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2 blommor</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 36109-2025 artfynd.xlsx
+++ b/artfynd/A 36109-2025 artfynd.xlsx
@@ -1217,41 +1217,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127300654</v>
+        <v>127300753</v>
       </c>
       <c r="B7" t="n">
-        <v>105484</v>
+        <v>98447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1260,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590948</v>
+        <v>590923</v>
       </c>
       <c r="R7" t="n">
-        <v>6418715</v>
+        <v>6418737</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,6 +1304,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2 blommor</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1323,49 +1336,41 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127300753</v>
+        <v>127300654</v>
       </c>
       <c r="B8" t="n">
-        <v>98447</v>
+        <v>105484</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1374,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590923</v>
+        <v>590948</v>
       </c>
       <c r="R8" t="n">
-        <v>6418737</v>
+        <v>6418715</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,11 +1415,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2 blommor</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 36109-2025 artfynd.xlsx
+++ b/artfynd/A 36109-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127093757</v>
       </c>
       <c r="B2" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127093589</v>
       </c>
       <c r="B3" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>127093718</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>127093875</v>
       </c>
       <c r="B5" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1217,49 +1217,41 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127300753</v>
+        <v>127300654</v>
       </c>
       <c r="B7" t="n">
-        <v>98447</v>
+        <v>105486</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1268,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590923</v>
+        <v>590948</v>
       </c>
       <c r="R7" t="n">
-        <v>6418737</v>
+        <v>6418715</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,11 +1296,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2 blommor</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,41 +1323,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127300654</v>
+        <v>127300753</v>
       </c>
       <c r="B8" t="n">
-        <v>105484</v>
+        <v>98448</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1379,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590948</v>
+        <v>590923</v>
       </c>
       <c r="R8" t="n">
-        <v>6418715</v>
+        <v>6418737</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,6 +1410,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2 blommor</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 36109-2025 artfynd.xlsx
+++ b/artfynd/A 36109-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127093757</v>
       </c>
       <c r="B2" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127093589</v>
       </c>
       <c r="B3" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>127093718</v>
       </c>
       <c r="B4" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>127093875</v>
       </c>
       <c r="B5" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>127300607</v>
       </c>
       <c r="B6" t="n">
-        <v>96050</v>
+        <v>96052</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>127300654</v>
       </c>
       <c r="B7" t="n">
-        <v>105486</v>
+        <v>105488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>127300753</v>
       </c>
       <c r="B8" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36109-2025 artfynd.xlsx
+++ b/artfynd/A 36109-2025 artfynd.xlsx
@@ -1217,41 +1217,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127300654</v>
+        <v>127300753</v>
       </c>
       <c r="B7" t="n">
-        <v>105488</v>
+        <v>98450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1260,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590948</v>
+        <v>590923</v>
       </c>
       <c r="R7" t="n">
-        <v>6418715</v>
+        <v>6418737</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,6 +1304,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2 blommor</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1323,49 +1336,41 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127300753</v>
+        <v>127300654</v>
       </c>
       <c r="B8" t="n">
-        <v>98450</v>
+        <v>105488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1374,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590923</v>
+        <v>590948</v>
       </c>
       <c r="R8" t="n">
-        <v>6418737</v>
+        <v>6418715</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,11 +1415,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2 blommor</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 36109-2025 artfynd.xlsx
+++ b/artfynd/A 36109-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127093757</v>
       </c>
       <c r="B2" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127093589</v>
       </c>
       <c r="B3" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>127093718</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>127093875</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>127300607</v>
       </c>
       <c r="B6" t="n">
-        <v>96052</v>
+        <v>96058</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,49 +1217,41 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127300753</v>
+        <v>127300654</v>
       </c>
       <c r="B7" t="n">
-        <v>98450</v>
+        <v>105494</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1268,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590923</v>
+        <v>590948</v>
       </c>
       <c r="R7" t="n">
-        <v>6418737</v>
+        <v>6418715</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,11 +1296,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2 blommor</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,41 +1323,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127300654</v>
+        <v>127300753</v>
       </c>
       <c r="B8" t="n">
-        <v>105488</v>
+        <v>98456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1379,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590948</v>
+        <v>590923</v>
       </c>
       <c r="R8" t="n">
-        <v>6418715</v>
+        <v>6418737</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,6 +1410,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2 blommor</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 36109-2025 artfynd.xlsx
+++ b/artfynd/A 36109-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127093757</v>
       </c>
       <c r="B2" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127093589</v>
       </c>
       <c r="B3" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>127093718</v>
       </c>
       <c r="B4" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>127093875</v>
       </c>
       <c r="B5" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>127300607</v>
       </c>
       <c r="B6" t="n">
-        <v>96058</v>
+        <v>96061</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>127300654</v>
       </c>
       <c r="B7" t="n">
-        <v>105494</v>
+        <v>105497</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>127300753</v>
       </c>
       <c r="B8" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36109-2025 artfynd.xlsx
+++ b/artfynd/A 36109-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127093757</v>
       </c>
       <c r="B2" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127093589</v>
       </c>
       <c r="B3" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>127093718</v>
       </c>
       <c r="B4" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>127093875</v>
       </c>
       <c r="B5" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>127300607</v>
       </c>
       <c r="B6" t="n">
-        <v>96061</v>
+        <v>96069</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>127300654</v>
       </c>
       <c r="B7" t="n">
-        <v>105497</v>
+        <v>105505</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>127300753</v>
       </c>
       <c r="B8" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36109-2025 artfynd.xlsx
+++ b/artfynd/A 36109-2025 artfynd.xlsx
@@ -1118,7 +1118,7 @@
         <v>127300607</v>
       </c>
       <c r="B6" t="n">
-        <v>96069</v>
+        <v>96070</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>127300654</v>
       </c>
       <c r="B7" t="n">
-        <v>105505</v>
+        <v>105506</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>127300753</v>
       </c>
       <c r="B8" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36109-2025 artfynd.xlsx
+++ b/artfynd/A 36109-2025 artfynd.xlsx
@@ -1217,41 +1217,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127300654</v>
+        <v>127300753</v>
       </c>
       <c r="B7" t="n">
-        <v>105506</v>
+        <v>98468</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1260,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590948</v>
+        <v>590923</v>
       </c>
       <c r="R7" t="n">
-        <v>6418715</v>
+        <v>6418737</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,6 +1304,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2 blommor</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1323,49 +1336,41 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127300753</v>
+        <v>127300654</v>
       </c>
       <c r="B8" t="n">
-        <v>98468</v>
+        <v>105506</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1374,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590923</v>
+        <v>590948</v>
       </c>
       <c r="R8" t="n">
-        <v>6418737</v>
+        <v>6418715</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,11 +1415,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2 blommor</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 36109-2025 artfynd.xlsx
+++ b/artfynd/A 36109-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1440,6 +1440,120 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128811224</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91877</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A 36109, Sandvik, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>590959</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6418696</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Liggande tallåga</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36109-2025 artfynd.xlsx
+++ b/artfynd/A 36109-2025 artfynd.xlsx
@@ -1445,7 +1445,7 @@
         <v>128811224</v>
       </c>
       <c r="B9" t="n">
-        <v>91877</v>
+        <v>91904</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36109-2025 artfynd.xlsx
+++ b/artfynd/A 36109-2025 artfynd.xlsx
@@ -1445,7 +1445,7 @@
         <v>128811224</v>
       </c>
       <c r="B9" t="n">
-        <v>91904</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36109-2025 artfynd.xlsx
+++ b/artfynd/A 36109-2025 artfynd.xlsx
@@ -1445,7 +1445,7 @@
         <v>128811224</v>
       </c>
       <c r="B9" t="n">
-        <v>91909</v>
+        <v>91914</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36109-2025 artfynd.xlsx
+++ b/artfynd/A 36109-2025 artfynd.xlsx
@@ -1445,7 +1445,7 @@
         <v>128811224</v>
       </c>
       <c r="B9" t="n">
-        <v>91914</v>
+        <v>91918</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36109-2025 artfynd.xlsx
+++ b/artfynd/A 36109-2025 artfynd.xlsx
@@ -1445,7 +1445,7 @@
         <v>128811224</v>
       </c>
       <c r="B9" t="n">
-        <v>91918</v>
+        <v>91923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36109-2025 artfynd.xlsx
+++ b/artfynd/A 36109-2025 artfynd.xlsx
@@ -1445,7 +1445,7 @@
         <v>128811224</v>
       </c>
       <c r="B9" t="n">
-        <v>91931</v>
+        <v>91934</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36109-2025 artfynd.xlsx
+++ b/artfynd/A 36109-2025 artfynd.xlsx
@@ -1445,7 +1445,7 @@
         <v>128811224</v>
       </c>
       <c r="B9" t="n">
-        <v>91934</v>
+        <v>91937</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36109-2025 artfynd.xlsx
+++ b/artfynd/A 36109-2025 artfynd.xlsx
@@ -1445,7 +1445,7 @@
         <v>128811224</v>
       </c>
       <c r="B9" t="n">
-        <v>91937</v>
+        <v>91944</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36109-2025 artfynd.xlsx
+++ b/artfynd/A 36109-2025 artfynd.xlsx
@@ -1445,7 +1445,7 @@
         <v>128811224</v>
       </c>
       <c r="B9" t="n">
-        <v>91944</v>
+        <v>91951</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36109-2025 artfynd.xlsx
+++ b/artfynd/A 36109-2025 artfynd.xlsx
@@ -1445,7 +1445,7 @@
         <v>128811224</v>
       </c>
       <c r="B9" t="n">
-        <v>91951</v>
+        <v>91953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36109-2025 artfynd.xlsx
+++ b/artfynd/A 36109-2025 artfynd.xlsx
@@ -1445,7 +1445,7 @@
         <v>128811224</v>
       </c>
       <c r="B9" t="n">
-        <v>91953</v>
+        <v>91962</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36109-2025 artfynd.xlsx
+++ b/artfynd/A 36109-2025 artfynd.xlsx
@@ -1445,7 +1445,7 @@
         <v>128811224</v>
       </c>
       <c r="B9" t="n">
-        <v>91962</v>
+        <v>91963</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36109-2025 artfynd.xlsx
+++ b/artfynd/A 36109-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127093757</v>
       </c>
       <c r="B2" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127093589</v>
       </c>
       <c r="B3" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>127093718</v>
       </c>
       <c r="B4" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>127093875</v>
       </c>
       <c r="B5" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>127300607</v>
       </c>
       <c r="B6" t="n">
-        <v>96071</v>
+        <v>96039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,49 +1217,41 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127300753</v>
+        <v>127300654</v>
       </c>
       <c r="B7" t="n">
-        <v>98469</v>
+        <v>105471</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1268,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590923</v>
+        <v>590948</v>
       </c>
       <c r="R7" t="n">
-        <v>6418737</v>
+        <v>6418715</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,11 +1296,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2 blommor</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,41 +1323,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127300654</v>
+        <v>127300753</v>
       </c>
       <c r="B8" t="n">
-        <v>105507</v>
+        <v>98436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1379,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590948</v>
+        <v>590923</v>
       </c>
       <c r="R8" t="n">
-        <v>6418715</v>
+        <v>6418737</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,6 +1410,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2 blommor</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 36109-2025 artfynd.xlsx
+++ b/artfynd/A 36109-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127093757</v>
       </c>
       <c r="B2" t="n">
-        <v>98436</v>
+        <v>98467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127093589</v>
       </c>
       <c r="B3" t="n">
-        <v>98436</v>
+        <v>98467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>127093718</v>
       </c>
       <c r="B4" t="n">
-        <v>98436</v>
+        <v>98467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>127093875</v>
       </c>
       <c r="B5" t="n">
-        <v>98436</v>
+        <v>98467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>127300607</v>
       </c>
       <c r="B6" t="n">
-        <v>96039</v>
+        <v>96071</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,41 +1217,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127300654</v>
+        <v>127300753</v>
       </c>
       <c r="B7" t="n">
-        <v>105471</v>
+        <v>98469</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1260,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590948</v>
+        <v>590923</v>
       </c>
       <c r="R7" t="n">
-        <v>6418715</v>
+        <v>6418737</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,6 +1304,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2 blommor</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1323,49 +1336,41 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127300753</v>
+        <v>127300654</v>
       </c>
       <c r="B8" t="n">
-        <v>98436</v>
+        <v>105507</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1374,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590923</v>
+        <v>590948</v>
       </c>
       <c r="R8" t="n">
-        <v>6418737</v>
+        <v>6418715</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,11 +1415,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2 blommor</t>
         </is>
       </c>
       <c r="AD8" t="b">
